--- a/out/LSTM-mamba2_repeat_2_000006.xlsx
+++ b/out/LSTM-mamba2_repeat_2_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.688844415955533</v>
+        <v>5.934848009080794</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.688844415955533</v>
+        <v>5.934848009080794</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.0143620844914687</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.0143620844914687</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.111245132341913</v>
+        <v>6.534848009080794</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.111245132341913</v>
+        <v>6.534848009080794</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.111245132341913</v>
+        <v>6.534848009080794</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.111245132341913</v>
+        <v>6.534848009080794</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.0143620844914687</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-2.947796454362106e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.03794043659060239</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.07595267473764415</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.008762006283272072</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.02914895234278671</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.02914895234278671</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.02909932070839033</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.152479114665589</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.3343611715954952</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.02917516050940805</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.2400098645215498</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.05110284301204655</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.3130551269550244</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.02798577649629558</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.3178798308855307</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.01155813490051347</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>0.3129811045179432</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.01440048802707511</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>0.3302264795559172</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>0.008668916992547373</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>0.333156208319707</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>0.006590346371295408</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>0.3376638378879528</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>0.002911350940306478</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>0.3368931316090294</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>0.002310390444566943</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.0002155096112694591</v>
+        <v>0.3386001318283172</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-0.00355491483402205</v>
+        <v>0.001143179440857017</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.004180053137960378</v>
+        <v>0.3385746396749492</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003778332695858744</v>
+        <v>0.0006612069707491649</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.003831303109081811</v>
+        <v>0.3387561787459376</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001888825734670103</v>
+        <v>0.0003295580857473972</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.003808431414494757</v>
+        <v>0.3387507621985364</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0008566716444626338</v>
+        <v>0.000158854945255757</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.003623910709094023</v>
+        <v>0.338741579781089</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0009965458735975191</v>
+        <v>9.179193055917936e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.00475741460940172</v>
+        <v>0.3387633463421946</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-0.0003670542499351367</v>
+        <v>2.624758159560671e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.003382897253362346</v>
+        <v>0.3387262037019806</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>1.07205380308973e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.003159931857949123</v>
+        <v>0.3387213914908343</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.001482201790229204</v>
+        <v>4.784784520434025e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.04113638665018987</v>
+        <v>0.3387179843933831</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.02728681541754526</v>
+        <v>0.3387126740162373</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.06103069573417481</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1271171423973264</v>
+        <v>0.3387087497298862</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.01511527225153327</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.0960835859390588</v>
+        <v>0.338708417626563</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.01638024339542514</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1136491947389145</v>
+        <v>0.3387087981616207</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.01083695269949765</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1188936513647239</v>
+        <v>0.3387090264826554</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.005939821850100438</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1199085224429006</v>
+        <v>0.3387091164273054</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1146789302116379</v>
+        <v>0.3387082584937205</v>
       </c>
     </row>
     <row r="74">
@@ -59763,21 +59763,21 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>0.0463667758718299</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1600565420708791</v>
+        <v>0.3387084868147552</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1600565420708791</v>
+        <v>0.3387076911505435</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1600565420708791</v>
+        <v>0.3387077534199166</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.159840493618398</v>
+        <v>0.3387077810951934</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>0.03138998468466261</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1912304783030604</v>
+        <v>0.3387079333092167</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.190951133728378</v>
+        <v>0.338707587368255</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0.0003843812062620082</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2138422609279594</v>
+        <v>0.3387076634752667</v>
       </c>
     </row>
     <row r="81">
@@ -65328,7 +65328,7 @@
         <v>0</v>
       </c>
       <c r="IY81" t="n">
-        <v>0.03534068713073427</v>
+        <v>0</v>
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2624825099522646</v>
+        <v>0.3387078295269282</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.04422923706165977</v>
+        <v>0</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3154078656122342</v>
+        <v>0.3387081893055283</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.02288104994637937</v>
+        <v>0</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3168049855312754</v>
+        <v>0.338708210061986</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.01335585569928764</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.320569801039787</v>
+        <v>0.3387083138442745</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.008784316357995642</v>
+        <v>0</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3247508955047373</v>
+        <v>0.3387085421653092</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.003816727259009336</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3235800120305931</v>
+        <v>0.338708417626563</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.001969303286006377</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3236953761902964</v>
+        <v>0.3387084453018399</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.001046004816845194</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3238144529569056</v>
+        <v>0.3387085006523938</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.0006727399765538945</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3241112796469112</v>
+        <v>0.3387087635675245</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.0003099043165362463</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3240572679094486</v>
+        <v>0.3387086805416937</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.0001220539091853538</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3239918079797907</v>
+        <v>0.3387084729771169</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>5.952206899021459e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3239885763583409</v>
+        <v>0.3387084868147552</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>3.223660648279602e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3239935528170471</v>
+        <v>0.33870862519114</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>8.518341954017061e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3239780005868909</v>
+        <v>0.3387083415195514</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>2.043047308558004e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3239696878251463</v>
+        <v>0.3387081685490706</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>-2.627008342686571e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3239636360012835</v>
+        <v>0.3387080647667821</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>-3.760561637792787e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3239593565282032</v>
+        <v>0.338708210061986</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>-4.138412736161525e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3239550797390824</v>
+        <v>0.3387084522206593</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>-4.311175652400717e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3239497307405451</v>
+        <v>0.3387082792501783</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3239494332313181</v>
+        <v>0.3387079817409513</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3239494193936796</v>
+        <v>0.3387079679033128</v>
       </c>
     </row>
     <row r="102">
@@ -82023,21 +82023,21 @@
         <v>0</v>
       </c>
       <c r="IY102" t="n">
-        <v>-4.988406284058349e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.3387076012058935</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.3387076012058935</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.3387075389365204</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.338707435154232</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.3387072621837512</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.3387073106154858</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.3387069508368857</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.3387069093239703</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.338706964674524</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3236005090661961</v>
+        <v>0.338707020025078</v>
       </c>
     </row>
     <row r="112">
@@ -89973,21 +89973,21 @@
         <v>0</v>
       </c>
       <c r="IY112" t="n">
-        <v>0.02106824891022547</v>
+        <v>0</v>
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3446687579764216</v>
+        <v>0.3387070615379933</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3446687579764216</v>
+        <v>0.3387067917040433</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3443170561207854</v>
+        <v>0.3387068470545972</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.0452016703724512</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.435316646529196</v>
+        <v>0.3387069923498011</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4242311470348509</v>
+        <v>0.3387069577557049</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4157737891819431</v>
+        <v>0.3387069439180663</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.04030600768593046</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4705448899312678</v>
+        <v>0.3387070338627165</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.06906284560325522</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5681376495923594</v>
+        <v>0.3387073521284011</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.02070921077297639</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5402849147489066</v>
+        <v>0.338707172239101</v>
       </c>
     </row>
     <row r="121">
@@ -97128,7 +97128,7 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>0.011949501893507</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5433939374758433</v>
+        <v>0.3387072137520164</v>
       </c>
     </row>
     <row r="122">
@@ -97923,7 +97923,7 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>0.002386171788813159</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5361687322217904</v>
+        <v>0.3387070269438971</v>
       </c>
     </row>
     <row r="123">
@@ -98718,7 +98718,7 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.001856547415774478</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5374790895291089</v>
+        <v>0.3387070961320896</v>
       </c>
     </row>
     <row r="124">
@@ -99513,21 +99513,21 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>-7.115499095726293e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5355304376315284</v>
+        <v>0.3387068954863318</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5355304376315284</v>
+        <v>0.3387069369992472</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.6143620844914687</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5355304376315284</v>
+        <v>0.338706964674524</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_2_000006.xlsx
+++ b/out/LSTM-mamba2_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.3523299884729494</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.111245132341913</v>
+        <v>0.2876904797093239</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.111245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915971</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915971</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915971</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915971</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915971</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915971</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915971</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915971</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915971</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915971</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915971</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.111245132341913</v>
+        <v>0.2876904797093239</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.3523299884729494</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.3523299884729494</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.111245132341913</v>
+        <v>0.2876904797093239</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.711245132341913</v>
+        <v>0.4876904797093239</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.1523299884729494</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.3523299884729494</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.3523299884729494</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.3523299884729494</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>-1.637170819088351e-05</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.05029726599179211</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.1006786390723626</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.009623877212098481</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.06955540347652626</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.01685691611045432</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.09365051151540643</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.009230087498750811</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.09524041676949546</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.003809082228720363</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>0.09362114564230432</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.004746789845737964</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>0.09930674315090082</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>0.002856766374601517</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>0.1002699255649962</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>0.002170691761274513</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>0.1017535647388303</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>0.0009565216996650787</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.1523299884729494</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>0.1014959720395505</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>0.0007592301794158865</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.1523299884729494</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.0002155096112694591</v>
+        <v>0.1020560440073546</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-0.00355491483402205</v>
+        <v>0.0003727235197590621</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.1523299884729494</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.004180053137960378</v>
+        <v>0.1020442818235361</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003778332695858744</v>
+        <v>0.0002160992566678451</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.7923504566552229</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.003831303109081811</v>
+        <v>0.1021010545109145</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001888825734670103</v>
+        <v>0.0001055496283339226</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.7923504566552229</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.003808431414494757</v>
+        <v>0.1020959168691647</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0008566716444626338</v>
+        <v>4.961831508525235e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.003623910709094023</v>
+        <v>0.1020895342613808</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0009965458735975191</v>
+        <v>2.503887500112463e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.00475741460940172</v>
+        <v>0.1020933046860606</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-0.0003670542499351367</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.3523299884729494</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.003382897253362346</v>
+        <v>0.1020772205327977</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-5.08417705457914e-07</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.711245132341913</v>
+        <v>0.4876904797093239</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.003159931857949123</v>
+        <v>0.1020722840707833</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.001482201790229204</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.04113638665018987</v>
+        <v>0.1020678829421783</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.02728681541754526</v>
+        <v>0.1020627277536055</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.06103069573417481</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1271171423973264</v>
+        <v>0.1020632674215056</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.01511527225153327</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.0960835859390588</v>
+        <v>0.1020629353181825</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.01638024339542514</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1136491947389145</v>
+        <v>0.1020633158532402</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.01083695269949765</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1188936513647239</v>
+        <v>0.1020635441742749</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.005939821850100438</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1199085224429006</v>
+        <v>0.1020636341189248</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.711245132341913</v>
+        <v>0.4876904797093239</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1146789302116379</v>
+        <v>0.10206277618534</v>
       </c>
     </row>
     <row r="74">
@@ -59763,21 +59763,21 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>0.0463667758718299</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.3523299884729494</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1600565420708791</v>
+        <v>0.1020630045063747</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1600565420708791</v>
+        <v>0.102062208842163</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.3523299884729494</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1600565420708791</v>
+        <v>0.1020622711115361</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.3523299884729494</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.159840493618398</v>
+        <v>0.1020622987868129</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>0.03138998468466261</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.688844415955533</v>
+        <v>0.2876904797093239</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1912304783030604</v>
+        <v>0.1020624510008362</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.711245132341913</v>
+        <v>0.2876904797093239</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.190951133728378</v>
+        <v>0.1020621050598745</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0.0003843812062620082</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2138422609279594</v>
+        <v>0.1020621811668861</v>
       </c>
     </row>
     <row r="81">
@@ -65328,7 +65328,7 @@
         <v>0</v>
       </c>
       <c r="IY81" t="n">
-        <v>0.03534068713073427</v>
+        <v>0</v>
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2624825099522646</v>
+        <v>0.1020623472185477</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.04422923706165977</v>
+        <v>0</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3154078656122342</v>
+        <v>0.1020627069971478</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.02288104994637937</v>
+        <v>0</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.711245132341913</v>
+        <v>0.4876904797093239</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3168049855312754</v>
+        <v>0.1020627277536055</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.01335585569928764</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.088844415955533</v>
+        <v>0.4876904797093239</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.320569801039787</v>
+        <v>0.102062831535894</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.008784316357995642</v>
+        <v>0</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.111245132341913</v>
+        <v>0.2876904797093239</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3247508955047373</v>
+        <v>0.1020630598569287</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.003816727259009336</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.111245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3235800120305931</v>
+        <v>0.1020629353181825</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.001969303286006377</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3236953761902964</v>
+        <v>0.1020629629934593</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.001046004816845194</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3238144529569056</v>
+        <v>0.1020630183440133</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.0006727399765538945</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3241112796469112</v>
+        <v>0.102063281259144</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.0003099043165362463</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3240572679094486</v>
+        <v>0.1020631982333132</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.0001220539091853538</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3239918079797907</v>
+        <v>0.1020629906687364</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>5.952206899021459e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3239885763583409</v>
+        <v>0.1020630045063747</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>3.223660648279602e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3239935528170471</v>
+        <v>0.1020631428827594</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>8.518341954017061e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.111245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3239780005868909</v>
+        <v>0.1020628592111708</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>2.043047308558004e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.111245132341913</v>
+        <v>0.2876904797093238</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3239696878251463</v>
+        <v>0.1020626862406901</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>-2.627008342686571e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.688844415955533</v>
+        <v>0.2876904797093239</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3239636360012835</v>
+        <v>0.1020625824584016</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>-3.760561637792787e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.111245132341913</v>
+        <v>0.2876904797093239</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3239593565282032</v>
+        <v>0.1020627277536055</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>-4.138412736161525e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915971</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3239550797390824</v>
+        <v>0.1020629699122787</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>-4.311175652400717e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.711245132341913</v>
+        <v>0.9277109478915971</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3239497307405451</v>
+        <v>0.1020627969417977</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.711245132341913</v>
+        <v>0.4876904797093239</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3239494332313181</v>
+        <v>0.1020624994325708</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.3523299884729494</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3239494193936796</v>
+        <v>0.1020624855949322</v>
       </c>
     </row>
     <row r="102">
@@ -82023,21 +82023,21 @@
         <v>0</v>
       </c>
       <c r="IY102" t="n">
-        <v>-4.988406284058349e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.102062118897513</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.102062118897513</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.1020620566281399</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.1020619528458514</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.1020617798753707</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.1020618283071052</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.1020614685285052</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.1020614270155898</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.1523299884729494</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3239440504523378</v>
+        <v>0.1020614823661435</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.1523299884729494</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3236005090661961</v>
+        <v>0.1020615377166974</v>
       </c>
     </row>
     <row r="112">
@@ -89973,21 +89973,21 @@
         <v>0</v>
       </c>
       <c r="IY112" t="n">
-        <v>0.02106824891022547</v>
+        <v>0</v>
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.1523299884729494</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3446687579764216</v>
+        <v>0.1020615792296128</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.1523299884729494</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3446687579764216</v>
+        <v>0.1020613093956627</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.711245132341913</v>
+        <v>0.4876904797093239</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3443170561207854</v>
+        <v>0.1020613647462167</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.0452016703724512</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.435316646529196</v>
+        <v>0.1020615100414206</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891597</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4242311470348509</v>
+        <v>0.1020614754473243</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.711245132341913</v>
+        <v>0.4876904797093239</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4157737891819431</v>
+        <v>0.1020614616096858</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.04030600768593046</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.1523299884729494</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4705448899312678</v>
+        <v>0.102061551554336</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.06906284560325522</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5681376495923594</v>
+        <v>0.1020618698200206</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.02070921077297639</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5402849147489066</v>
+        <v>0.1020616899307205</v>
       </c>
     </row>
     <row r="121">
@@ -97128,7 +97128,7 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>0.011949501893507</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5433939374758433</v>
+        <v>0.1020617314436359</v>
       </c>
     </row>
     <row r="122">
@@ -97923,7 +97923,7 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>0.002386171788813159</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5361687322217904</v>
+        <v>0.1020615446355166</v>
       </c>
     </row>
     <row r="123">
@@ -98718,7 +98718,7 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.001856547415774478</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5374790895291089</v>
+        <v>0.1020616138237091</v>
       </c>
     </row>
     <row r="124">
@@ -99513,21 +99513,21 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>-7.115499095726293e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5355304376315284</v>
+        <v>0.1020614131779512</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5355304376315284</v>
+        <v>0.1020614546908666</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.688844415955533</v>
+        <v>-0.9923504566552229</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5355304376315284</v>
+        <v>0.1020614823661435</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_2_000006.xlsx
+++ b/out/LSTM-mamba2_repeat_2_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.3434707522392273</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.2074083238840103</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.08326877653598785</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.01790056377649307</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3523299884729494</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.009053803980350494</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.2876904797093239</v>
+        <v>-0.16</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.01827471330761909</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.127710947891597</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.02281685173511505</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.01600008457899094</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.01090912520885468</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.01137062907218933</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01858912408351898</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.02344738692045212</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.02046659588813782</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.01986962556838989</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.02181699872016907</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.9277109478915971</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.02418327704071999</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.9277109478915971</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.023622065782547</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.9277109478915971</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01940731704235077</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.9277109478915971</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01202351227402687</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.9277109478915971</v>
+        <v>-0.16</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01231818646192551</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.9277109478915971</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01459912955760956</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.9277109478915971</v>
+        <v>-0.16</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.02140750363469124</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.9277109478915971</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.023442592471838</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.9277109478915971</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0173085518181324</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.9277109478915971</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0168442390859127</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.9277109478915971</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01318475976586342</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.2876904797093239</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0198858343064785</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3523299884729494</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.01995503902435303</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.01118530984967947</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.003989905118942261</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3523299884729494</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.002754300832748413</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.2876904797093239</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.008811410516500473</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.127710947891597</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.009841687977313995</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4876904797093239</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.005858452990651131</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1523299884729494</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.00673365592956543</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.003716450184583664</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.003213740885257721</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-1.335330307483673e-05</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3523299884729494</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0002009384334087372</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3523299884729494</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.006317658349871635</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3523299884729494</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.01582575216889381</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.02564655244350433</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.05417352542281151</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.07290048897266388</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.06305918097496033</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.04902459681034088</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.04157710075378418</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-1.637170819088351e-05</v>
+        <v>-1.572706125420518e-05</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.05029726599179211</v>
+        <v>0.0483169334537267</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.03840608149766922</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.1006786390723626</v>
+        <v>0.09671435015372233</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.009623877212098481</v>
+        <v>0.00924483870115754</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.04523739591240883</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.06955540347652626</v>
+        <v>0.06681670935983816</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01685691611045432</v>
+        <v>0.01619342928458149</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.04745631664991379</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.09365051151540643</v>
+        <v>0.08996313684407575</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.009230087498750811</v>
+        <v>0.008866366249509762</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.05651230365037918</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.09524041676949546</v>
+        <v>0.09149022721617087</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.003809082228720363</v>
+        <v>0.003659054835664152</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.03687077015638351</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.09362114564230432</v>
+        <v>0.08993453340209276</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.004746789845737964</v>
+        <v>0.004559387025061533</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0517066977918148</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.09930674315090082</v>
+        <v>0.09539572624475672</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.002856766374601517</v>
+        <v>0.002743335502610705</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.02415724098682404</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1002699255649962</v>
+        <v>0.09632073378365487</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.002170691761274513</v>
+        <v>0.002084454598152154</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.06265550851821899</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9923504566552229</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1017535647388303</v>
+        <v>0.09774598404177814</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0009565216996650787</v>
+        <v>0.0009199679821571501</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01628032699227333</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1523299884729494</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.1014959720395505</v>
+        <v>0.09749819371384895</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0007592301794158865</v>
+        <v>0.0007289636376568415</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.03945091739296913</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.1523299884729494</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.1020560440073546</v>
+        <v>0.09803588659381936</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0003727235197590621</v>
+        <v>0.0003577146381792318</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.05151155591011047</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1523299884729494</v>
+        <v>0.16</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.1020442818235361</v>
+        <v>0.09802439228128665</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0002160992566678451</v>
+        <v>0.0002073716544309565</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.06170477718114853</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7923504566552229</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.1021010545109145</v>
+        <v>0.09807872657311079</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0001055496283339226</v>
+        <v>9.973122684266348e-05</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.05370510742068291</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7923504566552229</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1020959168691647</v>
+        <v>0.0980735961756634</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>4.961831508525235e-05</v>
+        <v>4.674366692287064e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.0150039428845048</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9923504566552229</v>
+        <v>0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1020895342613808</v>
+        <v>0.0980672517426142</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.0176977775990963</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9923504566552229</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1020933046860606</v>
+        <v>0.09807102216729405</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.00515223853290081</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3523299884729494</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1020772205327977</v>
+        <v>0.09805493801403116</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.005358677357435226</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4876904797093239</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1020722840707833</v>
+        <v>0.09805000155201671</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01327532902359962</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1020678829421783</v>
+        <v>0.09804560042341171</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.02586937323212624</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1020627277536055</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01132449135184288</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1020632674215056</v>
+        <v>0.09804098490273906</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.02000337466597557</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1020629353181825</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.02547186240553856</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.127710947891597</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1020633158532402</v>
+        <v>0.09804103333447362</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.03140385448932648</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.127710947891597</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1020635441742749</v>
+        <v>0.0980412616555083</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01392362639307976</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.127710947891597</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1020636341189248</v>
+        <v>0.09804135160015826</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.01139384880661964</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4876904797093239</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.10206277618534</v>
+        <v>0.09804049366657343</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.007960109040141106</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3523299884729494</v>
+        <v>-0.16</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1020630045063747</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01712483540177345</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.16</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.102062208842163</v>
+        <v>0.09803992632339639</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.004088975489139557</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3523299884729494</v>
+        <v>-0.3</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1020622711115361</v>
+        <v>0.09803998859276948</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.00403558649122715</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3523299884729494</v>
+        <v>-0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1020622987868129</v>
+        <v>0.09804001626804634</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.0011284239590168</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2876904797093239</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1020624510008362</v>
+        <v>0.09804016848206963</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.0007996391505002975</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.2876904797093239</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1020621050598745</v>
+        <v>0.09803982254110789</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.005464561283588409</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.127710947891597</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1020621811668861</v>
+        <v>0.09803989864811953</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01381531357765198</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1020623472185477</v>
+        <v>0.09804006469978113</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01319020614027977</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.127710947891597</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1020627069971478</v>
+        <v>0.09804042447838117</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.001514945179224014</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.4876904797093239</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1020627277536055</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0007932931184768677</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.4876904797093239</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.102062831535894</v>
+        <v>0.09804054901712737</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01295414194464684</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2876904797093239</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1020630598569287</v>
+        <v>0.09804077733816206</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.02131257578730583</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.127710947891597</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1020629353181825</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.03290668874979019</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1020629629934593</v>
+        <v>0.09804068047469272</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.02188941091299057</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.127710947891597</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1020630183440133</v>
+        <v>0.09804073582524667</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.01597186550498009</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.127710947891597</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.102063281259144</v>
+        <v>0.09804099874037737</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01390209794044495</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.127710947891597</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1020631982333132</v>
+        <v>0.09804091571454657</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.02009481191635132</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.127710947891597</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1020629906687364</v>
+        <v>0.0980407081499698</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.02495462819933891</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.127710947891597</v>
+        <v>-0.16</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1020630045063747</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.02149736881256104</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.127710947891597</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1020631428827594</v>
+        <v>0.09804086036399286</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01072831079363823</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.127710947891597</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1020628592111708</v>
+        <v>0.09804057669240422</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.007274303585290909</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2876904797093238</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1020626862406901</v>
+        <v>0.09804040372192348</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-7.919594645500183e-05</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.2876904797093239</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1020625824584016</v>
+        <v>0.09804029993963498</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.009825091809034348</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.2876904797093239</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1020627277536055</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.01951923221349716</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.9277109478915971</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1020629699122787</v>
+        <v>0.09804068739351211</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.004820831120014191</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9277109478915971</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1020627969417977</v>
+        <v>0.09804051442303113</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.004156909883022308</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.4876904797093239</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1020624994325708</v>
+        <v>0.09804021691380418</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01145938783884048</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3523299884729494</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1020624855949322</v>
+        <v>0.09804020307616564</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.01044559851288795</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.102062118897513</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.005463797599077225</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.102062118897513</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.03044307976961136</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1020620566281399</v>
+        <v>0.09803977410937334</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01989175006747246</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1020619528458514</v>
+        <v>0.09803967032708484</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01254982128739357</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1020617798753707</v>
+        <v>0.09803949735660408</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01826514303684235</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1020618283071052</v>
+        <v>0.09803954578833864</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01815559342503548</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1020614685285052</v>
+        <v>0.0980391860097386</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.007275719195604324</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1020614270155898</v>
+        <v>0.09803914449682319</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.007620053365826607</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.1523299884729494</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1020614823661435</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.001301761716604233</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1523299884729494</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1020615377166974</v>
+        <v>0.09803925519793084</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-3.423728048801422e-05</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1523299884729494</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1020615792296128</v>
+        <v>0.09803929671084624</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.002335112541913986</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1523299884729494</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1020613093956627</v>
+        <v>0.09803902687689615</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.00239994004368782</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.4876904797093239</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1020613647462167</v>
+        <v>0.0980390822274501</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.003191765397787094</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.127710947891597</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1020615100414206</v>
+        <v>0.098039227522654</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.003904480487108231</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.127710947891597</v>
+        <v>0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1020614754473243</v>
+        <v>0.09803919292855776</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.003004919737577438</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.4876904797093239</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1020614616096858</v>
+        <v>0.09803917909091921</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.0009899046272039413</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.1523299884729494</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.102061551554336</v>
+        <v>0.09803926903556939</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.03300736844539642</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1020618698200206</v>
+        <v>0.09803958730125403</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.03018002584576607</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1020616899307205</v>
+        <v>0.0980394074119539</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.02104617655277252</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1020617314436359</v>
+        <v>0.09803944892486929</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.01103390753269196</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1020615446355166</v>
+        <v>0.09803926211675</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.004900721833109856</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9923504566552229</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1020616138237091</v>
+        <v>0.0980393313049425</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.007259085774421692</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9923504566552229</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1020614131779512</v>
+        <v>0.09803913065918465</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.0006669890135526657</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9923504566552229</v>
+        <v>0.7900000000000004</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1020614546908666</v>
+        <v>0.09803917217210005</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0008218660950660706</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9923504566552229</v>
+        <v>1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1020614823661435</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
   </sheetData>
